--- a/data/trans_dic/P1435-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1435-Provincia-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,24</t>
+          <t>2,01; 7,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,64</t>
+          <t>0,66; 4,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,92</t>
+          <t>0,69; 4,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,15</t>
+          <t>0,13; 1,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,24</t>
+          <t>2,01; 7,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,64</t>
+          <t>0,66; 4,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,92</t>
+          <t>0,69; 4,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,15</t>
+          <t>0,13; 1,32</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 20,42</t>
+          <t>13,87; 20,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,39</t>
+          <t>4,17; 8,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,86</t>
+          <t>0,19; 1,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,13</t>
+          <t>4,23; 8,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,07; 20,42</t>
+          <t>13,87; 20,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,39</t>
+          <t>4,17; 8,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,86</t>
+          <t>0,19; 1,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,13</t>
+          <t>4,23; 8,5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,28</t>
+          <t>2,91; 7,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,13</t>
+          <t>1,46; 5,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,1</t>
+          <t>1,09; 4,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,34</t>
+          <t>1,73; 5,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,28</t>
+          <t>2,91; 7,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,13</t>
+          <t>1,46; 5,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,1</t>
+          <t>1,09; 4,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,34</t>
+          <t>1,73; 5,48</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,12</t>
+          <t>5,01; 10,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,87</t>
+          <t>1,97; 6,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,93</t>
+          <t>0,45; 2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 48,91</t>
+          <t>2,36; 6,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,12</t>
+          <t>5,01; 10,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,87</t>
+          <t>1,97; 6,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,93</t>
+          <t>0,45; 2,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 48,91</t>
+          <t>2,36; 6,77</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,09</t>
+          <t>0,94; 6,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,4</t>
+          <t>5,04; 12,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,99</t>
+          <t>0,44; 4,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 12,04</t>
+          <t>6,47; 12,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,09</t>
+          <t>0,94; 6,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 12,4</t>
+          <t>5,04; 12,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,99</t>
+          <t>0,44; 4,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 12,04</t>
+          <t>6,47; 12,13</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,64; 12,23</t>
+          <t>5,32; 12,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 10,49</t>
+          <t>4,47; 10,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,45</t>
+          <t>2,47; 7,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,64; 12,23</t>
+          <t>5,32; 12,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 10,49</t>
+          <t>4,47; 10,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,45</t>
+          <t>2,47; 7,11</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,68</t>
+          <t>3,3; 6,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,43</t>
+          <t>2,52; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,57</t>
+          <t>3,09; 6,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,78</t>
+          <t>12,53; 18,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,68</t>
+          <t>3,3; 6,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,43</t>
+          <t>2,52; 5,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,57</t>
+          <t>3,09; 6,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,78</t>
+          <t>12,53; 18,02</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,96</t>
+          <t>6,01; 10,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,66</t>
+          <t>0,86; 2,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,83</t>
+          <t>0,47; 1,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,24</t>
+          <t>1,26; 3,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 9,96</t>
+          <t>6,01; 10,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,66</t>
+          <t>0,86; 2,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,83</t>
+          <t>0,47; 1,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,24</t>
+          <t>1,26; 3,22</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -1461,42 +1461,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,26; 4,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,39</t>
+          <t>1,46; 2,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,99</t>
+          <t>5,4; 6,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,61</t>
+          <t>6,84; 8,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,26; 4,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,39</t>
+          <t>1,46; 2,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,99</t>
+          <t>5,4; 6,96</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1433</t>
         </is>
       </c>
     </row>
@@ -1736,42 +1736,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5295; 18879</t>
+          <t>5240; 18832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1929; 13334</t>
+          <t>1888; 13141</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2795; 14206</t>
+          <t>1998; 13088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169; 3339</t>
+          <t>421; 4183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5295; 18879</t>
+          <t>5240; 18832</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1929; 13334</t>
+          <t>1888; 13141</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2795; 14206</t>
+          <t>1998; 13088</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>169; 3339</t>
+          <t>421; 4183</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>32684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>32684</t>
         </is>
       </c>
     </row>
@@ -1884,42 +1884,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70917; 102887</t>
+          <t>69885; 102998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21937; 43929</t>
+          <t>21827; 43614</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>984; 9753</t>
+          <t>982; 8872</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22289; 46592</t>
+          <t>22931; 46032</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70917; 102887</t>
+          <t>69885; 102998</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21937; 43929</t>
+          <t>21827; 43614</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>984; 9753</t>
+          <t>982; 8872</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22289; 46592</t>
+          <t>22931; 46032</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>10902</t>
         </is>
       </c>
     </row>
@@ -2032,42 +2032,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9669; 24403</t>
+          <t>9747; 24825</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4918; 17501</t>
+          <t>4962; 17337</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3599; 13805</t>
+          <t>3655; 14346</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5602; 18652</t>
+          <t>6161; 19535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9669; 24403</t>
+          <t>9747; 24825</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4918; 17501</t>
+          <t>4962; 17337</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3599; 13805</t>
+          <t>3655; 14346</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5602; 18652</t>
+          <t>6161; 19535</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>17784</t>
         </is>
       </c>
     </row>
@@ -2180,42 +2180,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17792; 37603</t>
+          <t>18603; 37347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7167; 22833</t>
+          <t>7649; 23462</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1827; 11335</t>
+          <t>1751; 10087</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12915; 232362</t>
+          <t>9957; 28522</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17792; 37603</t>
+          <t>18603; 37347</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7167; 22833</t>
+          <t>7649; 23462</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1827; 11335</t>
+          <t>1751; 10087</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12915; 232362</t>
+          <t>9957; 28522</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>20292</t>
         </is>
       </c>
     </row>
@@ -2328,42 +2328,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1902; 12654</t>
+          <t>1948; 13283</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10811; 27230</t>
+          <t>11061; 26385</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>960; 8711</t>
+          <t>961; 9506</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13270; 25076</t>
+          <t>14676; 27519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1902; 12654</t>
+          <t>1948; 13283</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10811; 27230</t>
+          <t>11061; 26385</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>960; 8711</t>
+          <t>961; 9506</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13270; 25076</t>
+          <t>14676; 27519</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11579</t>
         </is>
       </c>
     </row>
@@ -2476,42 +2476,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15694; 34008</t>
+          <t>14806; 33586</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12041; 29159</t>
+          <t>12435; 29873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 4650</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6764; 19092</t>
+          <t>6504; 18696</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15694; 34008</t>
+          <t>14806; 33586</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12041; 29159</t>
+          <t>12435; 29873</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 4650</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6764; 19092</t>
+          <t>6504; 18696</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95286</t>
+          <t>117066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>95286</t>
+          <t>117066</t>
         </is>
       </c>
     </row>
@@ -2624,42 +2624,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20679; 42654</t>
+          <t>21031; 43748</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17241; 37676</t>
+          <t>17496; 38349</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21505; 45436</t>
+          <t>21357; 43448</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44305; 133596</t>
+          <t>96181; 138364</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20679; 42654</t>
+          <t>21031; 43748</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17241; 37676</t>
+          <t>17496; 38349</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21505; 45436</t>
+          <t>21357; 43448</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44305; 133596</t>
+          <t>96181; 138364</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>17193</t>
         </is>
       </c>
     </row>
@@ -2772,42 +2772,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>47803; 78029</t>
+          <t>47063; 78406</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7211; 21848</t>
+          <t>7107; 21933</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3916; 15093</t>
+          <t>3885; 15209</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8805; 23214</t>
+          <t>10474; 26773</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>47803; 78029</t>
+          <t>47063; 78406</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7211; 21848</t>
+          <t>7107; 21933</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3916; 15093</t>
+          <t>3885; 15209</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8805; 23214</t>
+          <t>10474; 26773</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
     </row>
@@ -2920,42 +2920,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>116982; 162900</t>
+          <t>115776; 162178</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52831; 84756</t>
+          <t>51767; 83952</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>188999; 510642</t>
+          <t>201079; 259341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>229865; 290809</t>
+          <t>231258; 290641</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>116982; 162900</t>
+          <t>115776; 162178</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>52831; 84756</t>
+          <t>51767; 83952</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>188999; 510642</t>
+          <t>201079; 259341</t>
         </is>
       </c>
     </row>
